--- a/descrittive/statistiche_descrittive.xlsx
+++ b/descrittive/statistiche_descrittive.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4865,149 +4865,297 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C121" t="n">
-        <v>2.766170966503726</v>
+        <v>5.493516422874899</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9200727455675161</v>
+        <v>0.5340731428496249</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>3.526360524616162</v>
       </c>
       <c r="F121" t="n">
-        <v>2.167778818422124</v>
+        <v>5.204006687076795</v>
       </c>
       <c r="G121" t="n">
-        <v>2.673553765358734</v>
+        <v>5.521460917862246</v>
       </c>
       <c r="H121" t="n">
-        <v>3.5039708022539</v>
+        <v>5.842093037202379</v>
       </c>
       <c r="I121" t="n">
-        <v>4.804021044733257</v>
+        <v>6.816735880594968</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.04126662154704719</v>
+        <v>-0.8283806966850276</v>
       </c>
       <c r="K121" t="n">
-        <v>0.1578655222717176</v>
+        <v>2.303783644278041</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C122" t="n">
-        <v>2.733671763075938</v>
+        <v>5.263001122539428</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8039856860942876</v>
+        <v>0.4627145099498864</v>
       </c>
       <c r="E122" t="n">
-        <v>1.09861228866811</v>
+        <v>3.637586159726386</v>
       </c>
       <c r="F122" t="n">
-        <v>2.19722457733622</v>
+        <v>4.990432586778736</v>
       </c>
       <c r="G122" t="n">
-        <v>2.70805020110221</v>
+        <v>5.209486152841421</v>
       </c>
       <c r="H122" t="n">
-        <v>3.295836866004329</v>
+        <v>5.547081164359037</v>
       </c>
       <c r="I122" t="n">
-        <v>4.48863636973214</v>
+        <v>6.56244409369372</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.1302772747928893</v>
+        <v>0.0105271084823152</v>
       </c>
       <c r="K122" t="n">
-        <v>-0.4053176924666104</v>
+        <v>1.230203465692333</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>76</v>
       </c>
       <c r="C123" t="n">
-        <v>4.034126415923609</v>
+        <v>2.766170966503726</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6491750781860848</v>
+        <v>0.9200727455675161</v>
       </c>
       <c r="E123" t="n">
-        <v>2.19722457733622</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>3.630919097955846</v>
+        <v>2.167778818422124</v>
       </c>
       <c r="G123" t="n">
-        <v>4.142630567034474</v>
+        <v>2.673553765358734</v>
       </c>
       <c r="H123" t="n">
-        <v>4.524491306075094</v>
+        <v>3.5039708022539</v>
       </c>
       <c r="I123" t="n">
-        <v>5.402677381872279</v>
+        <v>4.804021044733257</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.5805354792093249</v>
+        <v>-0.04126662154704719</v>
       </c>
       <c r="K123" t="n">
-        <v>0.007670007665518952</v>
+        <v>0.1578655222717176</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PWM_ TE_POST_ln</t>
+          <t>PWM_ TP_POST_ln</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>81</v>
       </c>
       <c r="C124" t="n">
+        <v>2.733671763075938</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.8039856860942876</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.09861228866811</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.19722457733622</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.295836866004329</v>
+      </c>
+      <c r="I124" t="n">
+        <v>4.48863636973214</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.1302772747928893</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-0.4053176924666104</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>76</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.034126415923609</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.6491750781860848</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.19722457733622</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3.630919097955846</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.142630567034474</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4.524491306075094</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5.402677381872279</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.5805354792093249</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.007670007665518952</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TE_POST_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>81</v>
+      </c>
+      <c r="C126" t="n">
         <v>3.952882196686519</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D126" t="n">
         <v>0.6786102684429498</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E126" t="n">
         <v>1.6094379124341</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F126" t="n">
         <v>3.555348061489414</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G126" t="n">
         <v>4.007333185232471</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H126" t="n">
         <v>4.343805421853684</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I126" t="n">
         <v>5.225746673713202</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J126" t="n">
         <v>-0.6378988450226112</v>
       </c>
-      <c r="K124" t="n">
+      <c r="K126" t="n">
         <v>0.9408390526345167</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>84</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.356841875138777</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.6384352468329516</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.484906649788</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.965529864809449</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.460127707454046</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4.855906310553609</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.493061443340548</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.5867068386298385</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.108087113280869</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>86</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.232424334988723</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.6475468222270354</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.772588722239781</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3.876355832708575</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.276666119016055</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.682000999211238</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5.41164605185504</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.4837930671177115</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-0.2122574569570004</v>
       </c>
     </row>
   </sheetData>
@@ -5021,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9443,149 +9591,297 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C121" t="n">
-        <v>2.571794694448074</v>
+        <v>5.45640169448007</v>
       </c>
       <c r="D121" t="n">
-        <v>0.8098308055339752</v>
+        <v>0.4923477813782379</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>4.418840607796598</v>
       </c>
       <c r="F121" t="n">
-        <v>2.138333059508028</v>
+        <v>5.122199919033813</v>
       </c>
       <c r="G121" t="n">
-        <v>2.564949357461537</v>
+        <v>5.501049920602119</v>
       </c>
       <c r="H121" t="n">
-        <v>2.970085626360215</v>
+        <v>5.814875688859601</v>
       </c>
       <c r="I121" t="n">
-        <v>4.158883083359671</v>
+        <v>6.816735880594968</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.3900432675733084</v>
+        <v>0.117767995446664</v>
       </c>
       <c r="K121" t="n">
-        <v>1.114903107761535</v>
+        <v>0.1989399847554436</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C122" t="n">
-        <v>2.671055977396686</v>
+        <v>5.183050506371817</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8111173023642603</v>
+        <v>0.4926087644328399</v>
       </c>
       <c r="E122" t="n">
-        <v>1.09861228866811</v>
+        <v>3.637586159726386</v>
       </c>
       <c r="F122" t="n">
-        <v>2.079441541679836</v>
+        <v>4.930850681305049</v>
       </c>
       <c r="G122" t="n">
-        <v>2.484906649788</v>
+        <v>5.12076499216343</v>
       </c>
       <c r="H122" t="n">
-        <v>3.295836866004329</v>
+        <v>5.444407390648558</v>
       </c>
       <c r="I122" t="n">
-        <v>4.48863636973214</v>
+        <v>6.56244409369372</v>
       </c>
       <c r="J122" t="n">
-        <v>0.004122419568249248</v>
+        <v>0.08533994982012917</v>
       </c>
       <c r="K122" t="n">
-        <v>-0.4949468828487169</v>
+        <v>2.035762908210461</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>47</v>
       </c>
       <c r="C123" t="n">
-        <v>4.046872902028873</v>
+        <v>2.571794694448074</v>
       </c>
       <c r="D123" t="n">
-        <v>0.5954500176130887</v>
+        <v>0.8098308055339752</v>
       </c>
       <c r="E123" t="n">
-        <v>2.19722457733622</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>3.688879454113936</v>
+        <v>2.138333059508028</v>
       </c>
       <c r="G123" t="n">
-        <v>4.110873864173311</v>
+        <v>2.564949357461537</v>
       </c>
       <c r="H123" t="n">
-        <v>4.454347296253507</v>
+        <v>2.970085626360215</v>
       </c>
       <c r="I123" t="n">
-        <v>5.010635294096256</v>
+        <v>4.158883083359671</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.8771775591260569</v>
+        <v>-0.3900432675733084</v>
       </c>
       <c r="K123" t="n">
-        <v>0.9606341961119336</v>
+        <v>1.114903107761535</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PWM_ TE_POST_ln</t>
+          <t>PWM_ TP_POST_ln</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>48</v>
       </c>
       <c r="C124" t="n">
+        <v>2.671055977396686</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.8111173023642603</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.09861228866811</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.079441541679836</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.484906649788</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.295836866004329</v>
+      </c>
+      <c r="I124" t="n">
+        <v>4.48863636973214</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.004122419568249248</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-0.4949468828487169</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>47</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.046872902028873</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.5954500176130887</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.19722457733622</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3.688879454113936</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.110873864173311</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4.454347296253507</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5.010635294096256</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.8771775591260569</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.9606341961119336</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TE_POST_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>48</v>
+      </c>
+      <c r="C126" t="n">
         <v>3.855826570256667</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D126" t="n">
         <v>0.6136961751173914</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E126" t="n">
         <v>2.484906649788</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F126" t="n">
         <v>3.465735902799727</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G126" t="n">
         <v>3.960767816066775</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H126" t="n">
         <v>4.193414211367561</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I126" t="n">
         <v>5.225746673713202</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J126" t="n">
         <v>-0.2664908208810799</v>
       </c>
-      <c r="K124" t="n">
+      <c r="K126" t="n">
         <v>0.009320462264667206</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>50</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.304880531229997</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.5475997419198172</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.484906649788</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.97496494680516</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.388237894673161</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4.740585823154715</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.308267697401205</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.8050121856241567</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.224244429668152</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>50</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.143692423041294</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.624349064928297</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.772588722239781</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3.718325213028032</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.248495242049359</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.51085950651685</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5.375278407684165</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.4190339021686478</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-0.1146183639699681</v>
       </c>
     </row>
   </sheetData>
@@ -9599,7 +9895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14018,149 +14314,297 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C121" t="n">
-        <v>3.081194579835299</v>
+        <v>5.54300272740134</v>
       </c>
       <c r="D121" t="n">
-        <v>1.011864078194866</v>
+        <v>0.5880657568081431</v>
       </c>
       <c r="E121" t="n">
-        <v>1.09861228866811</v>
+        <v>3.526360524616162</v>
       </c>
       <c r="F121" t="n">
-        <v>2.19722457733622</v>
+        <v>5.290252675583094</v>
       </c>
       <c r="G121" t="n">
-        <v>3.044522437723423</v>
+        <v>5.552959584921617</v>
       </c>
       <c r="H121" t="n">
-        <v>3.761200115693562</v>
+        <v>5.962285716076737</v>
       </c>
       <c r="I121" t="n">
-        <v>4.804021044733257</v>
+        <v>6.331501849893691</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.1216966015387262</v>
+        <v>-1.68768412907481</v>
       </c>
       <c r="K121" t="n">
-        <v>-0.7929704515752412</v>
+        <v>4.550000999138656</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C122" t="n">
-        <v>2.824749269518486</v>
+        <v>5.369601944096244</v>
       </c>
       <c r="D122" t="n">
-        <v>0.7970193406706459</v>
+        <v>0.4012485951967238</v>
       </c>
       <c r="E122" t="n">
-        <v>1.09861228866811</v>
+        <v>4.68213122712422</v>
       </c>
       <c r="F122" t="n">
-        <v>2.302585092994046</v>
+        <v>5.049773817720299</v>
       </c>
       <c r="G122" t="n">
-        <v>2.772588722239781</v>
+        <v>5.272999558563747</v>
       </c>
       <c r="H122" t="n">
-        <v>3.332204510175204</v>
+        <v>5.730052344393323</v>
       </c>
       <c r="I122" t="n">
-        <v>4.290459441148391</v>
+        <v>6.107022887742255</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.3377483410555454</v>
+        <v>0.2501893434829616</v>
       </c>
       <c r="K122" t="n">
-        <v>0.03702551058754366</v>
+        <v>-1.114620395301887</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>29</v>
       </c>
       <c r="C123" t="n">
-        <v>4.013468317753012</v>
+        <v>3.081194579835299</v>
       </c>
       <c r="D123" t="n">
-        <v>0.738659879690803</v>
+        <v>1.011864078194866</v>
       </c>
       <c r="E123" t="n">
-        <v>2.564949357461537</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="F123" t="n">
-        <v>3.401197381662155</v>
+        <v>2.19722457733622</v>
       </c>
       <c r="G123" t="n">
-        <v>4.189654742026425</v>
+        <v>3.044522437723423</v>
       </c>
       <c r="H123" t="n">
-        <v>4.553876891600541</v>
+        <v>3.761200115693562</v>
       </c>
       <c r="I123" t="n">
-        <v>5.402677381872279</v>
+        <v>4.804021044733257</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.2968309564878643</v>
+        <v>-0.1216966015387262</v>
       </c>
       <c r="K123" t="n">
-        <v>-0.7544564577956758</v>
+        <v>-0.7929704515752412</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PWM_ TE_POST_ln</t>
+          <t>PWM_ TP_POST_ln</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>33</v>
       </c>
       <c r="C124" t="n">
+        <v>2.824749269518486</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.7970193406706459</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.09861228866811</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.772588722239781</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.332204510175204</v>
+      </c>
+      <c r="I124" t="n">
+        <v>4.290459441148391</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.3377483410555454</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.03702551058754366</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>29</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.013468317753012</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.738659879690803</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.564949357461537</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3.401197381662155</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.189654742026425</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4.553876891600541</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5.402677381872279</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.2968309564878643</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-0.7544564577956758</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TE_POST_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>33</v>
+      </c>
+      <c r="C126" t="n">
         <v>4.09405401694812</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D126" t="n">
         <v>0.7506215728032514</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E126" t="n">
         <v>1.6094379124341</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F126" t="n">
         <v>3.761200115693562</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G126" t="n">
         <v>4.07753744390572</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H126" t="n">
         <v>4.553876891600541</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I126" t="n">
         <v>5.204006687076795</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J126" t="n">
         <v>-1.204293970268617</v>
       </c>
-      <c r="K124" t="n">
+      <c r="K126" t="n">
         <v>2.564448252777431</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>34</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.433255616181099</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.7548595767061194</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.890371757896165</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.899199513410149</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.663261063132795</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5.008963047058558</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.493061443340548</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.6123522005403379</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.8728967228909732</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>36</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.355663101582373</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.6676340149007201</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.890371757896165</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.102539759106413</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.400132325655167</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.785893123976365</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5.41164605185504</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.6937745426482641</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.03472088355096847</v>
       </c>
     </row>
   </sheetData>
@@ -14411,7 +14855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16324,69 +16768,133 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.618142685568603</v>
+        <v>5.651997088576865</v>
       </c>
       <c r="C120" t="n">
-        <v>2.922200776138045</v>
+        <v>5.357675852273215</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1525147702803247</v>
+        <v>0.006624531762857252</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2.728970117043028</v>
+        <v>5.383318766572672</v>
       </c>
       <c r="C121" t="n">
-        <v>2.737826706081765</v>
+        <v>5.159871713368077</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9612984118276571</v>
+        <v>0.0209462138782065</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4.078605068174213</v>
+        <v>2.618142685568603</v>
       </c>
       <c r="C122" t="n">
-        <v>3.987243512200003</v>
+        <v>2.922200776138045</v>
       </c>
       <c r="D122" t="n">
-        <v>0.543877831923867</v>
+        <v>0.1525147702803247</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>PWM_ TP_POST_ln</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2.728970117043028</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2.737826706081765</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.9612984118276571</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>4.078605068174213</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.987243512200003</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.543877831923867</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>PWM_ TE_POST_ln</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B125" t="n">
         <v>4.041390571584374</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C125" t="n">
         <v>3.870695848567081</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D125" t="n">
         <v>0.261740933131584</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4.338826664701762</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.373219339172427</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.8053117859732313</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>4.326377823455423</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.146822267719061</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2033741866662731</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D123">
+  <conditionalFormatting sqref="D2:D127">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -16404,7 +16912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18676,81 +19184,157 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.962032710184285</v>
+        <v>3.450380226918088e-06</v>
       </c>
       <c r="C120" t="n">
-        <v>2.665588654719343</v>
+        <v>5.518563369846087</v>
       </c>
       <c r="D120" t="n">
-        <v>2.769495183582019</v>
+        <v>5.80375349700665</v>
       </c>
       <c r="E120" t="n">
-        <v>2.778539053709476</v>
+        <v>5.251244476526945</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2001922564006563</v>
+        <v>0.03999895118649846</v>
       </c>
       <c r="C121" t="n">
-        <v>3.272047062440462</v>
+        <v>5.31319230936888</v>
       </c>
       <c r="D121" t="n">
-        <v>2.752106998375001</v>
+        <v>5.402636544340353</v>
       </c>
       <c r="E121" t="n">
-        <v>2.644830383407166</v>
+        <v>5.149091586547535</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7278478240173624</v>
+        <v>0.962032710184285</v>
       </c>
       <c r="C122" t="n">
-        <v>3.969499377561634</v>
+        <v>2.665588654719343</v>
       </c>
       <c r="D122" t="n">
-        <v>4.110250422292581</v>
+        <v>2.769495183582019</v>
       </c>
       <c r="E122" t="n">
-        <v>3.989740221910723</v>
+        <v>2.778539053709476</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>PWM_ TP_POST_ln</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.2001922564006563</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.272047062440462</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2.752106998375001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.644830383407166</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.7278478240173624</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.969499377561634</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.110250422292581</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.989740221910723</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>PWM_ TE_POST_ln</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B125" t="n">
         <v>0.5881083778468047</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C125" t="n">
         <v>4.220792198189945</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D125" t="n">
         <v>3.955747370041696</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E125" t="n">
         <v>3.913367183747304</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.4085210700254769</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.254561051994603</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4.473098534312049</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.285224434830934</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.2091832336796663</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.617137984116359</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4.28407705822187</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.147045148574687</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B123">
+  <conditionalFormatting sqref="B2:B127">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -18768,7 +19352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21040,81 +21624,157 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PWM_ TP_PRE_ln</t>
+          <t>PLANNING_TR_PRE_ln</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6841073836544851</v>
+        <v>0.000291248215209529</v>
       </c>
       <c r="C120" t="n">
-        <v>2.937326758943186</v>
+        <v>5.64525043650492</v>
       </c>
       <c r="D120" t="n">
-        <v>2.691829573315883</v>
+        <v>5.626238228577164</v>
       </c>
       <c r="E120" t="n">
-        <v>2.797209824910826</v>
+        <v>5.148549610823102</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PWM_ TP_POST_ln</t>
+          <t>PLANNING_TR_POST_ln</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1289211111686107</v>
+        <v>0.112903432382746</v>
       </c>
       <c r="C121" t="n">
-        <v>3.059523973121554</v>
+        <v>5.418535767587162</v>
       </c>
       <c r="D121" t="n">
-        <v>2.682086960608673</v>
+        <v>5.278954489483191</v>
       </c>
       <c r="E121" t="n">
-        <v>2.568369689939829</v>
+        <v>5.126484512646504</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PWM_ TE_PRE_ln</t>
+          <t>PWM_ TP_PRE_ln</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.760958258420394</v>
+        <v>0.6841073836544851</v>
       </c>
       <c r="C122" t="n">
-        <v>4.036394081781737</v>
+        <v>2.937326758943186</v>
       </c>
       <c r="D122" t="n">
-        <v>4.077730388102227</v>
+        <v>2.691829573315883</v>
       </c>
       <c r="E122" t="n">
-        <v>3.947483073955177</v>
+        <v>2.797209824910826</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>PWM_ TP_POST_ln</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.1289211111686107</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.059523973121554</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2.682086960608673</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.568369689939829</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PWM_ TE_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.760958258420394</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.036394081781737</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.077730388102227</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.947483073955177</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>PWM_ TE_POST_ln</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B125" t="n">
         <v>0.4452684034897555</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C125" t="n">
         <v>4.130678502226164</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D125" t="n">
         <v>3.887028339360085</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E125" t="n">
         <v>3.928265709440594</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PWM_ TR_PRE_ln</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.5627606603315649</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.388764986242162</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4.408993273533841</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.238263213404597</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PWM_ TR_POST_ln</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.1159890189058746</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.512279410726657</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4.171441856065345</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.135818544205621</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B123">
+  <conditionalFormatting sqref="B2:B127">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
